--- a/Martin County Football Roster.xlsx
+++ b/Martin County Football Roster.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cw216\Desktop\Martin County Football\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{257368FE-8883-40B0-9360-3CA04E639723}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DD41B19-7D76-4C1F-8ECD-1FFCEA718919}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12" yWindow="732" windowWidth="23028" windowHeight="12084" xr2:uid="{709D5FDC-BCDF-4E52-917A-F0CD98921D43}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{709D5FDC-BCDF-4E52-917A-F0CD98921D43}"/>
   </bookViews>
   <sheets>
     <sheet name="Updated_Football_Roster" sheetId="1" r:id="rId1"/>
@@ -20,10 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="42">
-  <si>
-    <t>Number</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="47">
   <si>
     <t>Name</t>
   </si>
@@ -31,9 +28,6 @@
     <t>Position</t>
   </si>
   <si>
-    <t>Year</t>
-  </si>
-  <si>
     <t>Jerrod Haney</t>
   </si>
   <si>
@@ -55,69 +49,39 @@
     <t>QB, DB</t>
   </si>
   <si>
-    <t>Jaycob Bowman</t>
-  </si>
-  <si>
-    <t>Parker Maynard</t>
-  </si>
-  <si>
     <t>So.</t>
   </si>
   <si>
     <t>Jonothan Cline</t>
   </si>
   <si>
-    <t>RB, DB</t>
-  </si>
-  <si>
     <t>Brock Hedrick</t>
   </si>
   <si>
     <t>Gavin Stepp</t>
   </si>
   <si>
-    <t>Brody Mollett</t>
-  </si>
-  <si>
-    <t>Cole Jewell</t>
-  </si>
-  <si>
-    <t>FB, LB</t>
-  </si>
-  <si>
     <t>Jeremy Begley</t>
   </si>
   <si>
-    <t>TE, LB</t>
-  </si>
-  <si>
     <t>RB, LB</t>
   </si>
   <si>
     <t>Crayson Lafferty</t>
   </si>
   <si>
-    <t>Haskell Fuggett</t>
-  </si>
-  <si>
     <t>TE, DE</t>
   </si>
   <si>
     <t>Samuel Moore</t>
   </si>
   <si>
-    <t>TE, CB</t>
-  </si>
-  <si>
     <t>James Begley</t>
   </si>
   <si>
     <t>Brayden Fannin</t>
   </si>
   <si>
-    <t>Brayden Chapman</t>
-  </si>
-  <si>
     <t>OL, DL</t>
   </si>
   <si>
@@ -133,9 +97,6 @@
     <t>Braxton Moore</t>
   </si>
   <si>
-    <t>Payton Ward</t>
-  </si>
-  <si>
     <t>Bryson Osborne</t>
   </si>
   <si>
@@ -145,14 +106,68 @@
     <t>Braxton Carter</t>
   </si>
   <si>
-    <t>Bailey Crum</t>
+    <t>#</t>
+  </si>
+  <si>
+    <t>Yr.</t>
+  </si>
+  <si>
+    <t>Rex Ward</t>
+  </si>
+  <si>
+    <t>Dillion Daniel</t>
+  </si>
+  <si>
+    <t>Fr.</t>
+  </si>
+  <si>
+    <t>Noah Bowens</t>
+  </si>
+  <si>
+    <t>Ayden Warren</t>
+  </si>
+  <si>
+    <t>Liam Fields</t>
+  </si>
+  <si>
+    <t>Easton Slone</t>
+  </si>
+  <si>
+    <t>Dalton Vinson</t>
+  </si>
+  <si>
+    <t>Bradley Hatfield</t>
+  </si>
+  <si>
+    <t>Braxtin Cooke</t>
+  </si>
+  <si>
+    <t>Jason Newsome</t>
+  </si>
+  <si>
+    <t>Colton Mullins</t>
+  </si>
+  <si>
+    <t>Mason Newsome</t>
+  </si>
+  <si>
+    <t>Drake Hedrick</t>
+  </si>
+  <si>
+    <t>Sebastian Genovese</t>
+  </si>
+  <si>
+    <t>DL</t>
+  </si>
+  <si>
+    <t>Kenneth Staton</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -287,8 +302,21 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF030712"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF030712"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="33">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -466,6 +494,18 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE5E7EB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -629,8 +669,14 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1006,463 +1052,468 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5351C57-FDA9-4BAE-BD7B-12EC50102D58}">
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="1" max="1" width="8.83984375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="B1" t="s">
+    <row r="1" spans="1:4" ht="35.4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="2">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="2">
+        <v>3</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E1" t="s">
+      <c r="C3" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2">
+      <c r="D3" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="2">
+        <v>5</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="52.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="2">
+        <v>7</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D5" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="52.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="2">
+        <v>9</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="2">
+        <v>10</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D2" t="s">
+    </row>
+    <row r="8" spans="1:4" ht="52.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="2">
+        <v>11</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="2">
+        <v>12</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E2" t="s">
+      <c r="C9" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3">
+    <row r="10" spans="1:4" ht="52.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="2">
+        <v>15</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="2">
+        <v>20</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B3">
-        <v>7</v>
-      </c>
-      <c r="C3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4">
+      <c r="D11" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B4">
-        <v>11</v>
-      </c>
-      <c r="C4" t="s">
+    </row>
+    <row r="12" spans="1:4" ht="52.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="2">
+        <v>21</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="52.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="2">
+        <v>23</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5">
-        <v>8</v>
-      </c>
-      <c r="B5">
-        <v>13</v>
-      </c>
-      <c r="C5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" t="s">
-        <v>5</v>
-      </c>
-      <c r="E5" t="s">
+    </row>
+    <row r="14" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="2">
+        <v>24</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="2">
+        <v>28</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="2">
+        <v>30</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="2">
+        <v>32</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="2">
+        <v>38</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="52.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="2">
+        <v>44</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="2">
+        <v>50</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="52.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" s="2">
+        <v>53</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="52.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" s="2">
+        <v>55</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="2">
+        <v>57</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" s="2">
+        <v>60</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="52.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" s="2">
+        <v>62</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6">
+    <row r="26" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" s="2">
+        <v>65</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="52.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" s="2">
+        <v>70</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="52.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" s="2">
+        <v>72</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="52.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" s="2">
+        <v>73</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.55000000000000004">
+      <c r="A30" s="2">
+        <v>75</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D30" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B6">
-        <v>14</v>
-      </c>
-      <c r="C6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" t="s">
-        <v>5</v>
-      </c>
-      <c r="E6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7">
-        <v>11</v>
-      </c>
-      <c r="B7">
-        <v>16</v>
-      </c>
-      <c r="C7" t="s">
-        <v>14</v>
-      </c>
-      <c r="D7" t="s">
-        <v>15</v>
-      </c>
-      <c r="E7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8">
-        <v>12</v>
-      </c>
-      <c r="B8">
+    </row>
+    <row r="31" spans="1:4" ht="52.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31" s="2">
+        <v>77</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32" s="2">
+        <v>81</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="52.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" s="2">
+        <v>84</v>
+      </c>
+      <c r="B33" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D8" t="s">
-        <v>5</v>
-      </c>
-      <c r="E8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9">
-        <v>13</v>
-      </c>
-      <c r="B9">
-        <v>20</v>
-      </c>
-      <c r="C9" t="s">
-        <v>17</v>
-      </c>
-      <c r="D9" t="s">
-        <v>5</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10">
-        <v>14</v>
-      </c>
-      <c r="B10">
-        <v>21</v>
-      </c>
-      <c r="C10" t="s">
-        <v>18</v>
-      </c>
-      <c r="D10" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11">
-        <v>15</v>
-      </c>
-      <c r="B11">
-        <v>22</v>
-      </c>
-      <c r="C11" t="s">
-        <v>19</v>
-      </c>
-      <c r="D11" t="s">
-        <v>20</v>
-      </c>
-      <c r="E11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12">
-        <v>17</v>
-      </c>
-      <c r="B12">
-        <v>24</v>
-      </c>
-      <c r="C12" t="s">
-        <v>21</v>
-      </c>
-      <c r="D12" t="s">
-        <v>22</v>
-      </c>
-      <c r="E12" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14">
-        <v>19</v>
-      </c>
-      <c r="B14">
-        <v>28</v>
-      </c>
-      <c r="C14" t="s">
-        <v>24</v>
-      </c>
-      <c r="D14" t="s">
-        <v>23</v>
-      </c>
-      <c r="E14" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15">
-        <v>20</v>
-      </c>
-      <c r="B15">
-        <v>30</v>
-      </c>
-      <c r="C15" t="s">
-        <v>25</v>
-      </c>
-      <c r="D15" t="s">
-        <v>26</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16">
-        <v>21</v>
-      </c>
-      <c r="B16">
-        <v>34</v>
-      </c>
-      <c r="C16" t="s">
-        <v>27</v>
-      </c>
-      <c r="D16" t="s">
-        <v>28</v>
-      </c>
-      <c r="E16" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17">
-        <v>23</v>
-      </c>
-      <c r="B17">
-        <v>38</v>
-      </c>
-      <c r="C17" t="s">
-        <v>29</v>
-      </c>
-      <c r="D17" t="s">
-        <v>23</v>
-      </c>
-      <c r="E17" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18">
-        <v>24</v>
-      </c>
-      <c r="B18">
-        <v>44</v>
-      </c>
-      <c r="C18" t="s">
-        <v>30</v>
-      </c>
-      <c r="D18" t="s">
-        <v>26</v>
-      </c>
-      <c r="E18" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19">
-        <v>25</v>
-      </c>
-      <c r="B19">
-        <v>50</v>
-      </c>
-      <c r="C19" t="s">
-        <v>31</v>
-      </c>
-      <c r="D19" t="s">
+      <c r="C33" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="52.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34" s="2"/>
+      <c r="B34" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2" t="s">
         <v>32</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20">
-        <v>27</v>
-      </c>
-      <c r="B20">
-        <v>55</v>
-      </c>
-      <c r="C20" t="s">
-        <v>33</v>
-      </c>
-      <c r="D20" t="s">
-        <v>32</v>
-      </c>
-      <c r="E20" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21">
-        <v>28</v>
-      </c>
-      <c r="B21">
-        <v>56</v>
-      </c>
-      <c r="C21" t="s">
-        <v>34</v>
-      </c>
-      <c r="D21" t="s">
-        <v>32</v>
-      </c>
-      <c r="E21" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22">
-        <v>31</v>
-      </c>
-      <c r="B22">
-        <v>60</v>
-      </c>
-      <c r="C22" t="s">
-        <v>35</v>
-      </c>
-      <c r="D22" t="s">
-        <v>32</v>
-      </c>
-      <c r="E22" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23">
-        <v>32</v>
-      </c>
-      <c r="B23">
-        <v>62</v>
-      </c>
-      <c r="C23" t="s">
-        <v>36</v>
-      </c>
-      <c r="D23" t="s">
-        <v>32</v>
-      </c>
-      <c r="E23" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24">
-        <v>35</v>
-      </c>
-      <c r="B24">
-        <v>67</v>
-      </c>
-      <c r="C24" t="s">
-        <v>37</v>
-      </c>
-      <c r="D24" t="s">
-        <v>32</v>
-      </c>
-      <c r="E24" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25">
-        <v>36</v>
-      </c>
-      <c r="B25">
-        <v>70</v>
-      </c>
-      <c r="C25" t="s">
-        <v>38</v>
-      </c>
-      <c r="D25" t="s">
-        <v>32</v>
-      </c>
-      <c r="E25" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26">
-        <v>38</v>
-      </c>
-      <c r="B26">
-        <v>75</v>
-      </c>
-      <c r="C26" t="s">
-        <v>39</v>
-      </c>
-      <c r="D26" t="s">
-        <v>32</v>
-      </c>
-      <c r="E26" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27">
-        <v>39</v>
-      </c>
-      <c r="B27">
-        <v>77</v>
-      </c>
-      <c r="C27" t="s">
-        <v>40</v>
-      </c>
-      <c r="D27" t="s">
-        <v>32</v>
-      </c>
-      <c r="E27" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28">
-        <v>42</v>
-      </c>
-      <c r="B28">
-        <v>88</v>
-      </c>
-      <c r="C28" t="s">
-        <v>41</v>
-      </c>
-      <c r="D28" t="s">
-        <v>5</v>
-      </c>
-      <c r="E28" t="s">
-        <v>8</v>
       </c>
     </row>
   </sheetData>
